--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,6 +823,43 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ProtagonistEquipment</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Protagonist_ProtagonistEquipmentConfig</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>增加过程生成坟墓数量的主角装备</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BP_Head_Undead_0</t>
+          <t>BP_Head_Human</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>亡灵头部</t>
+          <t>人类头部</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Art_BP_Head_Undead_1</t>
+          <t>Art_BP_Head_Human</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>基础亡灵头部材料</t>
+          <t>案例躯体材料 BP_Head_Human</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
@@ -419,74 +419,74 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>ItemId</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>道具名</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>道具图标</t>
+          <t>IconAssetId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>道具类型</t>
+          <t>ItemType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>管理道具属性配置表</t>
+          <t>SourceTable</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>道具描述</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>售卖价格</t>
+          <t>SellPrice</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>主键；奖励系统公共 Id；CaptureLoot 等奖励字段只认本列</t>
+          <t>（待补 SPEC 中文说明）ItemId</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>道具公共展示名；未启用 i18n 时直接当展示串；空则 UI 回退 ItemId</t>
+          <t>（待补 SPEC 中文说明）DisplayName</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>奖励弹窗/通用掉落 UI 使用的专属图标资源 Id</t>
+          <t>（待补 SPEC 中文说明）IconAssetId</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Currency | Material | BodyPart | MagicBook | ProtagonistEquipment</t>
+          <t>（待补 SPEC 中文说明）ItemType</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>该道具权威来源表名；运行时据此校验与分发</t>
+          <t>（待补 SPEC 中文说明）SourceTable</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>通用描述文案；奖励展示优先取本列</t>
+          <t>（待补 SPEC 中文说明）Description</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>≥ 0；本轮仅存档与展示，未接出售系统时不驱动运行时</t>
+          <t>（待补 SPEC 中文说明）SellPrice</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
@@ -419,74 +419,74 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ItemId</t>
+          <t>道具ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DisplayName</t>
+          <t>道具名</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>IconAssetId</t>
+          <t>道具图标</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ItemType</t>
+          <t>道具类型</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>SourceTable</t>
+          <t>管理道具属性配置表</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>道具描述</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>SellPrice</t>
+          <t>售卖价格</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）ItemId</t>
+          <t>主键；奖励系统公共 Id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）DisplayName</t>
+          <t>道具公共展示名；空则 UI 回退 ItemId</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）IconAssetId</t>
+          <t>奖励弹窗/通用掉落 UI 图标资源 Id</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）ItemType</t>
+          <t>Currency | Material | BodyPart | MagicBook | ProtagonistEquipment</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）SourceTable</t>
+          <t>该道具权威来源表名；运行时据此校验与分发</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）Description</t>
+          <t>通用描述文案</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）SellPrice</t>
+          <t>≥ 0；商店出售入账精魂</t>
         </is>
       </c>
     </row>
